--- a/Assets/Resources/DataFiles/ExcelFile/Class/FighterStatData.xlsx
+++ b/Assets/Resources/DataFiles/ExcelFile/Class/FighterStatData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Project2\Assets\Resources\DataFiles\ExcelFile\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m\Documents\GitHub\Project2\Assets\Resources\DataFiles\ExcelFile\Class\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B7CB594-79C8-4247-8698-AE655F63C6FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7276A9C1-1AC9-4D04-AA23-37DC4E2E38D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A8CC0692-9D11-440E-B5CC-1903C5375D4B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A8CC0692-9D11-440E-B5CC-1903C5375D4B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,33 +34,61 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>float</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Damage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Defence</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Level</t>
+    <t>level</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>maxHP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>maxMP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>baseATK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>baseDEF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>baseAS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>baseMS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">float </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>baseCritRate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>baseCritMult</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>baseCDR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>baseMPRegen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>basePen</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -68,7 +96,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -84,6 +116,14 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -93,7 +133,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -101,18 +141,46 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -425,127 +493,519 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{621D28FC-4CAA-4AD9-88A5-FB70D9432676}">
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:N21"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="6" max="6" width="11.59765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="13.19921875" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="10.59765625" customWidth="1"/>
+    <col min="11" max="11" width="13.3984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A3" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="B3" s="3">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3">
+        <v>12</v>
+      </c>
+      <c r="D3" s="3">
+        <v>5</v>
+      </c>
+      <c r="E3" s="3">
+        <v>5</v>
+      </c>
+      <c r="F3" s="3">
+        <v>5</v>
+      </c>
+      <c r="G3" s="3">
+        <v>10</v>
+      </c>
+      <c r="H3" s="3">
+        <v>1</v>
+      </c>
+      <c r="I3" s="3">
+        <v>1</v>
+      </c>
+      <c r="J3" s="3">
+        <v>1</v>
+      </c>
+      <c r="K3" s="3">
+        <v>1</v>
+      </c>
+      <c r="L3" s="3">
+        <v>1</v>
+      </c>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3">
+        <v>15</v>
+      </c>
+      <c r="C4" s="3">
+        <v>14</v>
+      </c>
+      <c r="D4" s="3">
+        <v>7</v>
+      </c>
+      <c r="E4" s="3">
+        <v>7</v>
+      </c>
+      <c r="F4" s="3">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="G4" s="3">
+        <v>11</v>
+      </c>
+      <c r="H4" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="I4" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J4" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="K4" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="L4" s="3">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A5" s="2">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B5" s="3">
+        <v>20</v>
+      </c>
+      <c r="C5" s="3">
+        <v>16</v>
+      </c>
+      <c r="D5" s="3">
+        <v>10</v>
+      </c>
+      <c r="E5" s="3">
+        <v>9</v>
+      </c>
+      <c r="F5" s="3">
+        <v>7</v>
+      </c>
+      <c r="G5" s="3">
+        <v>12</v>
+      </c>
+      <c r="H5" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="I5" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="J5" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="K5" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="L5" s="3">
+        <v>3</v>
+      </c>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A6" s="2">
         <v>4</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B6" s="3">
+        <v>25</v>
+      </c>
+      <c r="C6" s="3">
+        <v>18</v>
+      </c>
+      <c r="D6" s="3">
+        <v>13</v>
+      </c>
+      <c r="E6" s="3">
+        <v>11</v>
+      </c>
+      <c r="F6" s="3">
+        <v>8</v>
+      </c>
+      <c r="G6" s="3">
+        <v>13</v>
+      </c>
+      <c r="H6" s="3">
+        <v>1.7</v>
+      </c>
+      <c r="I6" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="J6" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="K6" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="L6" s="3">
+        <v>4</v>
+      </c>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A7" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
+      <c r="B7" s="3">
+        <v>30</v>
+      </c>
+      <c r="C7" s="3">
+        <v>20</v>
+      </c>
+      <c r="D7" s="3">
+        <v>16</v>
+      </c>
+      <c r="E7" s="3">
+        <v>13</v>
+      </c>
+      <c r="F7" s="3">
+        <v>9</v>
+      </c>
+      <c r="G7" s="3">
+        <v>14</v>
+      </c>
+      <c r="H7" s="3">
+        <v>2</v>
+      </c>
+      <c r="I7" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="J7" s="3">
+        <v>1.8</v>
+      </c>
+      <c r="K7" s="3">
+        <v>1.8</v>
+      </c>
+      <c r="L7" s="3">
+        <v>5</v>
+      </c>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3">
+        <v>35</v>
+      </c>
+      <c r="C8" s="3">
+        <v>22</v>
+      </c>
+      <c r="D8" s="3">
+        <v>19</v>
+      </c>
+      <c r="E8" s="3">
+        <v>15</v>
+      </c>
+      <c r="F8" s="3">
         <v>10</v>
       </c>
-      <c r="C3">
+      <c r="G8" s="3">
+        <v>15</v>
+      </c>
+      <c r="H8" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="I8" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="J8" s="3">
+        <v>2</v>
+      </c>
+      <c r="K8" s="3">
+        <v>2</v>
+      </c>
+      <c r="L8" s="3">
+        <v>6</v>
+      </c>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3">
+        <v>40</v>
+      </c>
+      <c r="C9" s="3">
+        <v>24</v>
+      </c>
+      <c r="D9" s="3">
+        <v>22</v>
+      </c>
+      <c r="E9" s="3">
+        <v>17</v>
+      </c>
+      <c r="F9" s="3">
+        <v>11</v>
+      </c>
+      <c r="G9" s="3">
+        <v>16</v>
+      </c>
+      <c r="H9" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="I9" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="J9" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="K9" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="L9" s="3">
+        <v>7</v>
+      </c>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3">
+        <v>45</v>
+      </c>
+      <c r="C10" s="3">
+        <v>26</v>
+      </c>
+      <c r="D10" s="3">
+        <v>25</v>
+      </c>
+      <c r="E10" s="3">
+        <v>19</v>
+      </c>
+      <c r="F10" s="3">
         <v>12</v>
       </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="E3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>15</v>
-      </c>
-      <c r="C4">
+      <c r="G10" s="3">
+        <v>17</v>
+      </c>
+      <c r="H10" s="3">
+        <v>2.7</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1.7</v>
+      </c>
+      <c r="J10" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="K10" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="L10" s="3">
+        <v>8</v>
+      </c>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3">
+        <v>50</v>
+      </c>
+      <c r="C11" s="3">
+        <v>28</v>
+      </c>
+      <c r="D11" s="3">
+        <v>28</v>
+      </c>
+      <c r="E11" s="3">
+        <v>21</v>
+      </c>
+      <c r="F11" s="3">
+        <v>13</v>
+      </c>
+      <c r="G11" s="3">
+        <v>18</v>
+      </c>
+      <c r="H11" s="3">
+        <v>3</v>
+      </c>
+      <c r="I11" s="3">
+        <v>1.8</v>
+      </c>
+      <c r="J11" s="3">
+        <v>2.6</v>
+      </c>
+      <c r="K11" s="3">
+        <v>2.6</v>
+      </c>
+      <c r="L11" s="3">
+        <v>9</v>
+      </c>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+    </row>
+    <row r="12" spans="1:14" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="4">
+        <v>10</v>
+      </c>
+      <c r="B12" s="5">
+        <v>55</v>
+      </c>
+      <c r="C12" s="5">
+        <v>30</v>
+      </c>
+      <c r="D12" s="5">
+        <v>31</v>
+      </c>
+      <c r="E12" s="5">
+        <v>23</v>
+      </c>
+      <c r="F12" s="5">
         <v>14</v>
       </c>
-      <c r="D4">
-        <v>7</v>
-      </c>
-      <c r="E4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5">
-        <v>20</v>
-      </c>
-      <c r="C5">
-        <v>16</v>
-      </c>
-      <c r="D5">
-        <v>9</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6">
-        <v>25</v>
-      </c>
-      <c r="C6">
-        <v>18</v>
-      </c>
-      <c r="D6">
-        <v>11</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>30</v>
-      </c>
-      <c r="C7">
-        <v>20</v>
-      </c>
-      <c r="D7">
-        <v>13</v>
-      </c>
-      <c r="E7">
-        <v>9</v>
-      </c>
+      <c r="G12" s="5">
+        <v>19</v>
+      </c>
+      <c r="H12" s="5">
+        <v>3.2</v>
+      </c>
+      <c r="I12" s="5">
+        <v>1.9</v>
+      </c>
+      <c r="J12" s="5">
+        <v>2.8</v>
+      </c>
+      <c r="K12" s="5">
+        <v>2.8</v>
+      </c>
+      <c r="L12" s="5">
+        <v>10</v>
+      </c>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G16" s="3"/>
+    </row>
+    <row r="17" spans="7:7" x14ac:dyDescent="0.4">
+      <c r="G17" s="3"/>
+    </row>
+    <row r="18" spans="7:7" x14ac:dyDescent="0.4">
+      <c r="G18" s="3"/>
+    </row>
+    <row r="19" spans="7:7" x14ac:dyDescent="0.4">
+      <c r="G19" s="3"/>
+    </row>
+    <row r="20" spans="7:7" x14ac:dyDescent="0.4">
+      <c r="G20" s="3"/>
+    </row>
+    <row r="21" spans="7:7" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="G21" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
